--- a/administrative_forms/002_crisis_communication_form--administrative_forms.xlsx
+++ b/administrative_forms/002_crisis_communication_form--administrative_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,10 +525,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Emergency Type</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>What kind of crisis are we facing?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please choose emergency type.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -548,10 +552,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>incident_location</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>What location is the incident at?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Provide exact location details.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -561,17 +569,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>contact_person</t>
+          <t>contact_person_name</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>contact_person</t>
+          <t>Who do we need to contact?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +597,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>contact_email</t>
+          <t>contact_person_email</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>contact_email</t>
+          <t>Contact person's email</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +620,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>contact_phone</t>
+          <t>contact_person_phone</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>contact_phone</t>
+          <t>Contact person's phone</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -640,7 +648,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>emergency_details</t>
+          <t>Emergency Details</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +666,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>contact_person</t>
+          <t>contact_method</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>contact_person</t>
+          <t>How would you like to be contacted?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +684,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>contact_email</t>
+          <t>category</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>contact_email</t>
+          <t>Category of emergency</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +712,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>contact_phone</t>
+          <t>emergency_description</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>contact_phone</t>
+          <t>Emergency Description</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +730,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>emergency_details</t>
+          <t>contact_person</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>emergency_details</t>
+          <t>Contact person</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,16 +758,177 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>contact_method_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>Contact method</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>response_time</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Response time</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>response_date</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Response date</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>contact_status</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Contact status</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>contact_status_label</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Contact status label</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>contact_person_2</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Contact Person 2</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>contact_status_2</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Contact Status 2</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>response_date_2</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Response Date 2</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -776,12 +945,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -804,102 +973,204 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>contact_person_choices</t>
+          <t>contact_method_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>contact_person_choices</t>
+          <t>contact_method_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>contact_person_choices</t>
+          <t>category_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>fire</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>contact_person_choices</t>
+          <t>category_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>police</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Police</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>contact_person_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>option_a</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Option A</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>contact_person_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>option_b</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Option B</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>contact_method_2_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>option_a</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>contact_method_2_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>option_b</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>contact_person_2_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>option_a</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>contact_person_2_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>option_b</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>contact_status_2_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>option_a</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>contact_status_2_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>option_b</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Option B</t>
         </is>
       </c>
     </row>
